--- a/Acoustics/Exam_1_Folder/Crossover_speakers.xlsx
+++ b/Acoustics/Exam_1_Folder/Crossover_speakers.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="65" documentId="11_A8D22E52E8D70D729C46777B7253018143ACC4B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B13DF022-422C-4A64-AE2C-AF1F55A06174}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="11_A8D22E52E8D70D729C46777B7253018143ACC4B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D09F3A96-E8A0-456D-BB99-B8B662A67C18}"/>
   <bookViews>
     <workbookView xWindow="12120" yWindow="0" windowWidth="12686" windowHeight="13251" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,10 +438,10 @@
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="12.84375" customWidth="1"/>
-    <col min="4" max="4" width="11.921875" customWidth="1"/>
-    <col min="5" max="5" width="12.921875" customWidth="1"/>
-    <col min="7" max="7" width="15.84375" customWidth="1"/>
+    <col min="3" max="3" width="14.15234375" customWidth="1"/>
+    <col min="4" max="4" width="13.53515625" customWidth="1"/>
+    <col min="5" max="5" width="14.23046875" customWidth="1"/>
+    <col min="7" max="7" width="16.84375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.4">

--- a/Acoustics/Exam_1_Folder/Crossover_speakers.xlsx
+++ b/Acoustics/Exam_1_Folder/Crossover_speakers.xlsx
@@ -3,19 +3,32 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="69" documentId="11_A8D22E52E8D70D729C46777B7253018143ACC4B4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D09F3A96-E8A0-456D-BB99-B8B662A67C18}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{5E20306C-FAB0-453A-9668-33AA51F4A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12120" yWindow="0" windowWidth="12686" windowHeight="13251" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="13372" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>DataPtNum</t>
   </si>
@@ -26,9 +39,6 @@
     <t>phase</t>
   </si>
   <si>
-    <t>Gain (|Vin/Vout|)</t>
-  </si>
-  <si>
     <t>Vin(FuncGen)</t>
   </si>
   <si>
@@ -37,11 +47,20 @@
   <si>
     <t>Vout(LoPass)</t>
   </si>
+  <si>
+    <t>HiPassGain (|Vout/Vi|)</t>
+  </si>
+  <si>
+    <t>LoPassGain (|Vout/Vin|)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -87,10 +106,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,17 +454,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="14.15234375" customWidth="1"/>
-    <col min="4" max="4" width="13.53515625" customWidth="1"/>
-    <col min="5" max="5" width="14.23046875" customWidth="1"/>
-    <col min="7" max="7" width="16.84375" customWidth="1"/>
+    <col min="3" max="3" width="11.84375" customWidth="1"/>
+    <col min="4" max="4" width="12.23046875" customWidth="1"/>
+    <col min="5" max="5" width="13.53515625" customWidth="1"/>
+    <col min="6" max="6" width="7.4609375" customWidth="1"/>
+    <col min="7" max="7" width="21.4609375" customWidth="1"/>
+    <col min="8" max="8" width="19.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,411 +474,1394 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C2">
+        <v>0.8</v>
+      </c>
+      <c r="D2">
+        <v>0.62</v>
+      </c>
+      <c r="E2">
+        <v>0.02</v>
+      </c>
+      <c r="F2">
+        <v>-15</v>
+      </c>
+      <c r="G2" s="3">
+        <f>D2/C2</f>
+        <v>0.77499999999999991</v>
+      </c>
+      <c r="H2" s="3">
+        <f>E2/C2</f>
+        <v>2.4999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C3">
+        <v>0.88</v>
+      </c>
+      <c r="D3">
+        <v>0.6</v>
+      </c>
+      <c r="E3">
+        <v>0.02</v>
+      </c>
+      <c r="F3">
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="G3" s="3">
+        <f t="shared" ref="G3:G50" si="0">D3/C3</f>
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="H3" s="3">
+        <f t="shared" ref="H3:H50" si="1">E3/C3</f>
+        <v>2.2727272727272728E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C4">
+        <v>0.88</v>
+      </c>
+      <c r="D4">
+        <v>0.6</v>
+      </c>
+      <c r="E4">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F4">
+        <v>-18</v>
+      </c>
+      <c r="G4" s="3">
+        <f t="shared" si="0"/>
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0454545454545454E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C5">
+        <v>0.88</v>
+      </c>
+      <c r="D5">
+        <v>0.64</v>
+      </c>
+      <c r="E5">
+        <v>0.02</v>
+      </c>
+      <c r="F5">
+        <v>-10</v>
+      </c>
+      <c r="G5" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2727272727272728E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C6">
+        <v>0.88</v>
+      </c>
+      <c r="D6">
+        <v>0.64</v>
+      </c>
+      <c r="E6">
+        <v>0.02</v>
+      </c>
+      <c r="F6">
+        <v>-20</v>
+      </c>
+      <c r="G6" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="1"/>
+        <v>2.2727272727272728E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C7">
+        <v>0.88</v>
+      </c>
+      <c r="D7">
+        <v>0.64</v>
+      </c>
+      <c r="E7">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F7">
+        <v>-12</v>
+      </c>
+      <c r="G7" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H7" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0454545454545454E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C8">
+        <v>0.88</v>
+      </c>
+      <c r="D8">
+        <v>0.64</v>
+      </c>
+      <c r="E8">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F8">
+        <v>-12.8</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9318181818181821E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>75</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C9">
+        <v>0.88</v>
+      </c>
+      <c r="D9">
+        <v>0.64</v>
+      </c>
+      <c r="E9">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F9">
+        <v>-14</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9318181818181821E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C10">
+        <v>0.88</v>
+      </c>
+      <c r="D10">
+        <v>0.64</v>
+      </c>
+      <c r="E10">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F10">
+        <v>-15</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0454545454545454E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C11">
+        <v>0.88</v>
+      </c>
+      <c r="D11">
+        <v>0.64</v>
+      </c>
+      <c r="E11">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F11">
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="G11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0454545454545454E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
         <v>90</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C12">
+        <v>0.88</v>
+      </c>
+      <c r="D12">
+        <v>0.64</v>
+      </c>
+      <c r="E12">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F12">
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="G12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0454545454545454E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
         <v>95</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C13">
+        <v>0.88</v>
+      </c>
+      <c r="D13">
+        <v>0.64</v>
+      </c>
+      <c r="E13">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F13">
+        <v>-18</v>
+      </c>
+      <c r="G13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0454545454545454E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C14">
+        <v>0.86</v>
+      </c>
+      <c r="D14">
+        <v>0.66</v>
+      </c>
+      <c r="E14">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F14">
+        <v>-18</v>
+      </c>
+      <c r="G14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.76744186046511631</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="1"/>
+        <v>2.0930232558139535E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
         <v>150</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C15">
+        <v>0.86</v>
+      </c>
+      <c r="D15">
+        <v>0.66</v>
+      </c>
+      <c r="E15">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F15">
+        <v>-25.7</v>
+      </c>
+      <c r="G15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.76744186046511631</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9767441860465119E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
         <v>200</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C16">
+        <v>0.88</v>
+      </c>
+      <c r="D16">
+        <v>0.68</v>
+      </c>
+      <c r="E16">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F16">
+        <v>-13.9</v>
+      </c>
+      <c r="G16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.77272727272727282</v>
+      </c>
+      <c r="H16" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7045454545454544E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
         <v>250</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C17">
+        <v>0.92</v>
+      </c>
+      <c r="D17">
+        <v>0.68</v>
+      </c>
+      <c r="E17">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="F17">
+        <v>-18</v>
+      </c>
+      <c r="G17" s="3">
+        <f t="shared" si="0"/>
+        <v>0.73913043478260876</v>
+      </c>
+      <c r="H17" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6304347826086956E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
         <v>300</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C18">
+        <v>0.92</v>
+      </c>
+      <c r="D18">
+        <v>0.68</v>
+      </c>
+      <c r="E18">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F18">
+        <v>-22.5</v>
+      </c>
+      <c r="G18" s="3">
+        <f t="shared" si="0"/>
+        <v>0.73913043478260876</v>
+      </c>
+      <c r="H18" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9565217391304346E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
         <v>350</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C19">
+        <v>0.92</v>
+      </c>
+      <c r="D19">
+        <v>0.68</v>
+      </c>
+      <c r="E19">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F19">
+        <v>-25.7</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="0"/>
+        <v>0.73913043478260876</v>
+      </c>
+      <c r="H19" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7391304347826087E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
         <v>400</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C20">
+        <v>0.96</v>
+      </c>
+      <c r="D20">
+        <v>0.72</v>
+      </c>
+      <c r="E20">
+        <v>1.9E-2</v>
+      </c>
+      <c r="F20">
+        <v>-30</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="H20" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9791666666666666E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
         <v>450</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C21">
+        <v>1.04</v>
+      </c>
+      <c r="D21">
+        <v>0.72</v>
+      </c>
+      <c r="E21">
+        <v>2.7E-2</v>
+      </c>
+      <c r="F21">
+        <v>-36</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="1"/>
+        <v>2.596153846153846E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
         <v>500</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C22">
+        <v>1.04</v>
+      </c>
+      <c r="D22">
+        <v>0.72</v>
+      </c>
+      <c r="E22">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="F22">
+        <v>-36</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="0"/>
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="1"/>
+        <v>3.5576923076923075E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
         <v>550</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C23">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D23">
+        <v>0.72</v>
+      </c>
+      <c r="E23">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="F23">
+        <v>-45</v>
+      </c>
+      <c r="G23" s="3">
+        <f t="shared" si="0"/>
+        <v>0.64285714285714279</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="1"/>
+        <v>4.2857142857142851E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
         <v>600</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C24">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="D24">
+        <v>0.8</v>
+      </c>
+      <c r="E24">
+        <v>6.2E-2</v>
+      </c>
+      <c r="F24">
+        <v>-45</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" si="0"/>
+        <v>0.68965517241379315</v>
+      </c>
+      <c r="H24" s="3">
+        <f t="shared" si="1"/>
+        <v>5.3448275862068968E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
         <v>650</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C25">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="D25">
+        <v>0.8</v>
+      </c>
+      <c r="E25">
+        <v>0.08</v>
+      </c>
+      <c r="F25">
+        <v>-45</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.68965517241379315</v>
+      </c>
+      <c r="H25" s="3">
+        <f t="shared" si="1"/>
+        <v>6.8965517241379323E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
         <v>700</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C26">
+        <v>1.28</v>
+      </c>
+      <c r="D26">
+        <v>0.82</v>
+      </c>
+      <c r="E26">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="F26">
+        <v>45</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="0"/>
+        <v>0.640625</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="1"/>
+        <v>7.421875E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
         <v>750</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C27">
+        <v>1.28</v>
+      </c>
+      <c r="D27">
+        <v>0.84</v>
+      </c>
+      <c r="E27">
+        <v>0.12</v>
+      </c>
+      <c r="F27">
+        <v>-60</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="0"/>
+        <v>0.65625</v>
+      </c>
+      <c r="H27" s="3">
+        <f t="shared" si="1"/>
+        <v>9.375E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
         <v>800</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C28">
+        <v>1.4</v>
+      </c>
+      <c r="D28">
+        <v>0.9</v>
+      </c>
+      <c r="E28">
+        <v>0.16</v>
+      </c>
+      <c r="F28">
+        <v>-60</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="0"/>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="1"/>
+        <v>0.1142857142857143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
         <v>850</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C29">
+        <v>1.44</v>
+      </c>
+      <c r="D29">
+        <v>0.92</v>
+      </c>
+      <c r="E29">
+        <v>0.192</v>
+      </c>
+      <c r="F29">
+        <v>-60</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" si="0"/>
+        <v>0.63888888888888895</v>
+      </c>
+      <c r="H29" s="3">
+        <f t="shared" si="1"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
         <v>900</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C30">
+        <v>1.52</v>
+      </c>
+      <c r="D30">
+        <v>0.96</v>
+      </c>
+      <c r="E30">
+        <v>0.216</v>
+      </c>
+      <c r="F30">
+        <v>-60</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="0"/>
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="H30" s="3">
+        <f t="shared" si="1"/>
+        <v>0.14210526315789473</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
         <v>950</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C31">
+        <v>1.6</v>
+      </c>
+      <c r="D31">
+        <v>1.04</v>
+      </c>
+      <c r="E31">
+        <v>0.25</v>
+      </c>
+      <c r="F31">
+        <v>54</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="H31" s="3">
+        <f t="shared" si="1"/>
+        <v>0.15625</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32">
         <v>1000</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C32">
+        <v>1.68</v>
+      </c>
+      <c r="D32">
+        <v>1.08</v>
+      </c>
+      <c r="E32">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="F32">
+        <v>-18</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="0"/>
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="1"/>
+        <v>0.17142857142857143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
         <v>1500</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C33">
+        <v>0.92</v>
+      </c>
+      <c r="D33">
+        <v>1.04</v>
+      </c>
+      <c r="E33">
+        <v>0.34</v>
+      </c>
+      <c r="F33">
+        <v>90</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1304347826086956</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.36956521739130438</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
         <v>2000</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C34">
+        <v>1.2</v>
+      </c>
+      <c r="D34">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E34">
+        <v>0.9</v>
+      </c>
+      <c r="F34">
+        <v>72</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="0"/>
+        <v>0.46666666666666673</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
         <v>2500</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C35">
+        <v>0.88</v>
+      </c>
+      <c r="D35">
+        <v>0.26</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>135</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="0"/>
+        <v>0.29545454545454547</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1363636363636365</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
         <v>3000</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C36">
+        <v>0.76</v>
+      </c>
+      <c r="D36">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="E36">
+        <v>1.04</v>
+      </c>
+      <c r="F36">
+        <v>103.6</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="0"/>
+        <v>0.21578947368421053</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="1"/>
+        <v>1.368421052631579</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
         <v>3500</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C37">
+        <v>0.76</v>
+      </c>
+      <c r="D37">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E37">
+        <v>1.08</v>
+      </c>
+      <c r="F37">
+        <v>96.4</v>
+      </c>
+      <c r="G37" s="3">
+        <f t="shared" si="0"/>
+        <v>0.18421052631578949</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="1"/>
+        <v>1.4210526315789473</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
         <v>4000</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C38">
+        <v>0.82</v>
+      </c>
+      <c r="D38">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="E38">
+        <v>1.08</v>
+      </c>
+      <c r="F38">
+        <v>108</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" si="0"/>
+        <v>0.16097560975609757</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3170731707317074</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
         <v>4500</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C39">
+        <v>0.88</v>
+      </c>
+      <c r="D39">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="E39">
+        <v>1.2</v>
+      </c>
+      <c r="F39">
+        <v>122</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3636363636363635</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
         <v>5000</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C40">
+        <v>0.98</v>
+      </c>
+      <c r="D40">
+        <v>0.128</v>
+      </c>
+      <c r="E40">
+        <v>1.24</v>
+      </c>
+      <c r="F40">
+        <v>99</v>
+      </c>
+      <c r="G40" s="3">
+        <f t="shared" si="0"/>
+        <v>0.1306122448979592</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2653061224489797</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
         <v>5500</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C41">
+        <v>1.06</v>
+      </c>
+      <c r="D41">
+        <v>0.12</v>
+      </c>
+      <c r="E41">
+        <v>1.28</v>
+      </c>
+      <c r="F41">
+        <v>110</v>
+      </c>
+      <c r="G41" s="3">
+        <f t="shared" si="0"/>
+        <v>0.11320754716981131</v>
+      </c>
+      <c r="H41" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2075471698113207</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
         <v>6000</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C42">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="D42">
+        <v>0.12</v>
+      </c>
+      <c r="E42">
+        <v>1.32</v>
+      </c>
+      <c r="F42">
+        <v>116.5</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" si="0"/>
+        <v>0.10714285714285712</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1785714285714286</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
         <v>6500</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C43">
+        <v>1.18</v>
+      </c>
+      <c r="D43">
+        <v>0.16</v>
+      </c>
+      <c r="E43">
+        <v>1.32</v>
+      </c>
+      <c r="F43">
+        <v>108</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" si="0"/>
+        <v>0.13559322033898305</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1186440677966103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
         <v>7000</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C44">
+        <v>1.28</v>
+      </c>
+      <c r="D44">
+        <v>0.104</v>
+      </c>
+      <c r="E44">
+        <v>1.48</v>
+      </c>
+      <c r="F44">
+        <v>108</v>
+      </c>
+      <c r="G44" s="3">
+        <f t="shared" si="0"/>
+        <v>8.1249999999999989E-2</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" si="1"/>
+        <v>1.15625</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
         <v>7500</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C45">
+        <v>1.32</v>
+      </c>
+      <c r="D45">
+        <v>0.1</v>
+      </c>
+      <c r="E45">
+        <v>1.48</v>
+      </c>
+      <c r="F45">
+        <v>115.7</v>
+      </c>
+      <c r="G45" s="3">
+        <f t="shared" si="0"/>
+        <v>7.575757575757576E-2</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1212121212121211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46">
         <v>8000</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C46">
+        <v>1.4</v>
+      </c>
+      <c r="D46">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="E46">
+        <v>1.52</v>
+      </c>
+      <c r="F46">
+        <v>125</v>
+      </c>
+      <c r="G46" s="3">
+        <f t="shared" si="0"/>
+        <v>6.5714285714285711E-2</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="1"/>
+        <v>1.0857142857142859</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47">
         <v>8500</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C47">
+        <v>1.46</v>
+      </c>
+      <c r="D47">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="E47">
+        <v>1.56</v>
+      </c>
+      <c r="F47">
+        <v>105</v>
+      </c>
+      <c r="G47" s="3">
+        <f t="shared" si="0"/>
+        <v>6.0273972602739721E-2</v>
+      </c>
+      <c r="H47" s="3">
+        <f t="shared" si="1"/>
+        <v>1.0684931506849316</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
         <v>9000</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C48">
+        <v>1.48</v>
+      </c>
+      <c r="D48">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="E48">
+        <v>1.64</v>
+      </c>
+      <c r="F48">
+        <v>147</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" si="0"/>
+        <v>5.675675675675676E-2</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1081081081081081</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49">
         <v>9500</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C49">
+        <v>1.56</v>
+      </c>
+      <c r="D49">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="E49">
+        <v>1.72</v>
+      </c>
+      <c r="F49">
+        <v>162</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" si="0"/>
+        <v>4.8717948717948718E-2</v>
+      </c>
+      <c r="H49" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1025641025641024</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50">
         <v>10000</v>
+      </c>
+      <c r="C50">
+        <v>1.6</v>
+      </c>
+      <c r="D50">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="E50">
+        <v>1.72</v>
+      </c>
+      <c r="F50">
+        <v>90</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="0"/>
+        <v>4.7499999999999994E-2</v>
+      </c>
+      <c r="H50" s="3">
+        <f t="shared" si="1"/>
+        <v>1.075</v>
       </c>
     </row>
   </sheetData>

--- a/Acoustics/Exam_1_Folder/Crossover_speakers.xlsx
+++ b/Acoustics/Exam_1_Folder/Crossover_speakers.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{5E20306C-FAB0-453A-9668-33AA51F4A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="14_{5E20306C-FAB0-453A-9668-33AA51F4A8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{310235EA-8526-46C2-B521-1A4946229EBB}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="13372" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -126,10 +126,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -461,7 +457,7 @@
     <col min="3" max="3" width="11.84375" customWidth="1"/>
     <col min="4" max="4" width="12.23046875" customWidth="1"/>
     <col min="5" max="5" width="13.53515625" customWidth="1"/>
-    <col min="6" max="6" width="7.4609375" customWidth="1"/>
+    <col min="6" max="6" width="9.69140625" customWidth="1"/>
     <col min="7" max="7" width="21.4609375" customWidth="1"/>
     <col min="8" max="8" width="19.53515625" customWidth="1"/>
   </cols>
@@ -500,24 +496,24 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="D2">
-        <v>0.62</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="E2">
-        <v>0.02</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="F2">
-        <v>-15</v>
+        <v>-171</v>
       </c>
       <c r="G2" s="3">
         <f>D2/C2</f>
-        <v>0.77499999999999991</v>
+        <v>0.88800000000000012</v>
       </c>
       <c r="H2" s="3">
         <f>E2/C2</f>
-        <v>2.4999999999999998E-2</v>
+        <v>6.8000000000000005E-3</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -528,24 +524,24 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>0.88</v>
+        <v>2.62</v>
       </c>
       <c r="D3">
-        <v>0.6</v>
+        <v>2.38</v>
       </c>
       <c r="E3">
-        <v>0.02</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="F3">
-        <v>-16.399999999999999</v>
+        <v>-160</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" ref="G3:G50" si="0">D3/C3</f>
-        <v>0.68181818181818177</v>
+        <v>0.90839694656488545</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H50" si="1">E3/C3</f>
-        <v>2.2727272727272728E-2</v>
+        <v>6.8702290076335867E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -556,24 +552,24 @@
         <v>50</v>
       </c>
       <c r="C4">
-        <v>0.88</v>
+        <v>2.4</v>
       </c>
       <c r="D4">
-        <v>0.6</v>
+        <v>2.14</v>
       </c>
       <c r="E4">
-        <v>1.7999999999999999E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="F4">
-        <v>-18</v>
+        <v>-151</v>
       </c>
       <c r="G4" s="3">
         <f t="shared" si="0"/>
-        <v>0.68181818181818177</v>
+        <v>0.89166666666666672</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="1"/>
-        <v>2.0454545454545454E-2</v>
+        <v>7.9166666666666673E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -584,24 +580,24 @@
         <v>55</v>
       </c>
       <c r="C5">
-        <v>0.88</v>
+        <v>2.12</v>
       </c>
       <c r="D5">
-        <v>0.64</v>
+        <v>1.86</v>
       </c>
       <c r="E5">
         <v>0.02</v>
       </c>
       <c r="F5">
-        <v>-10</v>
+        <v>148</v>
       </c>
       <c r="G5" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.87735849056603776</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="1"/>
-        <v>2.2727272727272728E-2</v>
+        <v>9.433962264150943E-3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -612,24 +608,24 @@
         <v>60</v>
       </c>
       <c r="C6">
-        <v>0.88</v>
+        <v>1.86</v>
       </c>
       <c r="D6">
-        <v>0.64</v>
+        <v>1.6</v>
       </c>
       <c r="E6">
         <v>0.02</v>
       </c>
       <c r="F6">
-        <v>-20</v>
+        <v>-95</v>
       </c>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.86021505376344087</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="1"/>
-        <v>2.2727272727272728E-2</v>
+        <v>1.075268817204301E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -640,24 +636,24 @@
         <v>65</v>
       </c>
       <c r="C7">
-        <v>0.88</v>
+        <v>1.66</v>
       </c>
       <c r="D7">
-        <v>0.64</v>
+        <v>1.44</v>
       </c>
       <c r="E7">
-        <v>1.7999999999999999E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F7">
-        <v>-12</v>
+        <v>-78.7</v>
       </c>
       <c r="G7" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.86746987951807231</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="1"/>
-        <v>2.0454545454545454E-2</v>
+        <v>1.2650602409638556E-2</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -668,24 +664,24 @@
         <v>70</v>
       </c>
       <c r="C8">
-        <v>0.88</v>
+        <v>1.52</v>
       </c>
       <c r="D8">
-        <v>0.64</v>
+        <v>1.3</v>
       </c>
       <c r="E8">
-        <v>1.7000000000000001E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F8">
-        <v>-12.8</v>
+        <v>-90</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.85526315789473684</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="1"/>
-        <v>1.9318181818181821E-2</v>
+        <v>1.3815789473684212E-2</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -696,24 +692,24 @@
         <v>75</v>
       </c>
       <c r="C9">
-        <v>0.88</v>
+        <v>1.42</v>
       </c>
       <c r="D9">
-        <v>0.64</v>
+        <v>1.2</v>
       </c>
       <c r="E9">
-        <v>1.7000000000000001E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F9">
-        <v>-14</v>
+        <v>-71</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.84507042253521125</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="1"/>
-        <v>1.9318181818181821E-2</v>
+        <v>1.4788732394366198E-2</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -724,24 +720,24 @@
         <v>80</v>
       </c>
       <c r="C10">
-        <v>0.88</v>
+        <v>1.34</v>
       </c>
       <c r="D10">
-        <v>0.64</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E10">
-        <v>1.7999999999999999E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F10">
-        <v>-15</v>
+        <v>-63</v>
       </c>
       <c r="G10" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.82089552238805974</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="1"/>
-        <v>2.0454545454545454E-2</v>
+        <v>1.5671641791044775E-2</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -752,24 +748,24 @@
         <v>85</v>
       </c>
       <c r="C11">
-        <v>0.88</v>
+        <v>1.3</v>
       </c>
       <c r="D11">
-        <v>0.64</v>
+        <v>1.06</v>
       </c>
       <c r="E11">
-        <v>1.7999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="F11">
-        <v>-16.399999999999999</v>
+        <v>-80</v>
       </c>
       <c r="G11" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.81538461538461537</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="1"/>
-        <v>2.0454545454545454E-2</v>
+        <v>1.5384615384615384E-2</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -780,24 +776,24 @@
         <v>90</v>
       </c>
       <c r="C12">
-        <v>0.88</v>
+        <v>1.28</v>
       </c>
       <c r="D12">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>1.7999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="F12">
-        <v>-16.399999999999999</v>
+        <v>-81.8</v>
       </c>
       <c r="G12" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.78125</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="1"/>
-        <v>2.0454545454545454E-2</v>
+        <v>1.5625E-2</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -808,24 +804,24 @@
         <v>95</v>
       </c>
       <c r="C13">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="D13">
-        <v>0.64</v>
+        <v>0.98</v>
       </c>
       <c r="E13">
-        <v>1.7999999999999999E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="F13">
-        <v>-18</v>
+        <v>-114</v>
       </c>
       <c r="G13" s="3">
         <f t="shared" si="0"/>
-        <v>0.72727272727272729</v>
+        <v>0.80327868852459017</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="1"/>
-        <v>2.0454545454545454E-2</v>
+        <v>1.5573770491803279E-2</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -836,24 +832,24 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0.86</v>
+        <v>1.19</v>
       </c>
       <c r="D14">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="E14">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="F14">
-        <v>-18</v>
+        <v>154</v>
       </c>
       <c r="G14" s="3">
         <f t="shared" si="0"/>
-        <v>0.76744186046511631</v>
+        <v>0.74789915966386555</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="1"/>
-        <v>2.0930232558139535E-2</v>
+        <v>1.5126050420168067E-2</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -864,24 +860,24 @@
         <v>150</v>
       </c>
       <c r="C15">
-        <v>0.86</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D15">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="E15">
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="F15">
-        <v>-25.7</v>
+        <v>152</v>
       </c>
       <c r="G15" s="3">
         <f t="shared" si="0"/>
-        <v>0.76744186046511631</v>
+        <v>0.71818181818181814</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="1"/>
-        <v>1.9767441860465119E-2</v>
+        <v>1.5454545454545455E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -892,24 +888,24 @@
         <v>200</v>
       </c>
       <c r="C16">
-        <v>0.88</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="D16">
-        <v>0.68</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="E16">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="F16">
-        <v>-13.9</v>
+        <v>172</v>
       </c>
       <c r="G16" s="3">
         <f t="shared" si="0"/>
-        <v>0.77272727272727282</v>
+        <v>0.69909909909909906</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="1"/>
-        <v>1.7045454545454544E-2</v>
+        <v>1.3513513513513513E-2</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -920,24 +916,24 @@
         <v>250</v>
       </c>
       <c r="C17">
-        <v>0.92</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="D17">
-        <v>0.68</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="E17">
-        <v>1.4999999999999999E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F17">
-        <v>-18</v>
+        <v>80</v>
       </c>
       <c r="G17" s="3">
         <f t="shared" si="0"/>
-        <v>0.73913043478260876</v>
+        <v>0.68070175438596503</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="1"/>
-        <v>1.6304347826086956E-2</v>
+        <v>1.2280701754385967E-2</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -948,24 +944,24 @@
         <v>300</v>
       </c>
       <c r="C18">
-        <v>0.92</v>
+        <v>1.17</v>
       </c>
       <c r="D18">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="E18">
-        <v>1.7999999999999999E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="F18">
-        <v>-22.5</v>
+        <v>87</v>
       </c>
       <c r="G18" s="3">
         <f t="shared" si="0"/>
-        <v>0.73913043478260876</v>
+        <v>0.68376068376068388</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="1"/>
-        <v>1.9565217391304346E-2</v>
+        <v>1.4529914529914532E-2</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -976,24 +972,24 @@
         <v>350</v>
       </c>
       <c r="C19">
-        <v>0.92</v>
+        <v>1.21</v>
       </c>
       <c r="D19">
-        <v>0.68</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="E19">
-        <v>1.6E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="F19">
-        <v>-25.7</v>
+        <v>147</v>
       </c>
       <c r="G19" s="3">
         <f t="shared" si="0"/>
-        <v>0.73913043478260876</v>
+        <v>0.68099173553719006</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="1"/>
-        <v>1.7391304347826087E-2</v>
+        <v>1.735537190082645E-2</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -1004,24 +1000,24 @@
         <v>400</v>
       </c>
       <c r="C20">
-        <v>0.96</v>
+        <v>1.26</v>
       </c>
       <c r="D20">
-        <v>0.72</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="E20">
-        <v>1.9E-2</v>
+        <v>0.03</v>
       </c>
       <c r="F20">
-        <v>-30</v>
+        <v>-151</v>
       </c>
       <c r="G20" s="3">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>0.67936507936507939</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="1"/>
-        <v>1.9791666666666666E-2</v>
+        <v>2.3809523809523808E-2</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -1032,24 +1028,24 @@
         <v>450</v>
       </c>
       <c r="C21">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="D21">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="E21">
-        <v>2.7E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="F21">
-        <v>-36</v>
+        <v>-155</v>
       </c>
       <c r="G21" s="3">
         <f t="shared" si="0"/>
-        <v>0.69230769230769229</v>
+        <v>0.67692307692307685</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="1"/>
-        <v>2.596153846153846E-2</v>
+        <v>2.923076923076923E-2</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -1060,24 +1056,24 @@
         <v>500</v>
       </c>
       <c r="C22">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="D22">
-        <v>0.72</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="E22">
-        <v>3.6999999999999998E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F22">
-        <v>-36</v>
+        <v>-153</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
-        <v>0.69230769230769229</v>
+        <v>0.66962962962962957</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="1"/>
-        <v>3.5576923076923075E-2</v>
+        <v>3.7037037037037035E-2</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
@@ -1088,24 +1084,24 @@
         <v>550</v>
       </c>
       <c r="C23">
-        <v>1.1200000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="D23">
-        <v>0.72</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="E23">
-        <v>4.8000000000000001E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="F23">
-        <v>-45</v>
+        <v>-150</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="0"/>
-        <v>0.64285714285714279</v>
+        <v>0.66857142857142871</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="1"/>
-        <v>4.2857142857142851E-2</v>
+        <v>4.5000000000000005E-2</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -1116,24 +1112,24 @@
         <v>600</v>
       </c>
       <c r="C24">
-        <v>1.1599999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="D24">
-        <v>0.8</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="E24">
-        <v>6.2E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="F24">
-        <v>-45</v>
+        <v>-168</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="0"/>
-        <v>0.68965517241379315</v>
+        <v>0.67397260273972603</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="1"/>
-        <v>5.3448275862068968E-2</v>
+        <v>5.2739726027397259E-2</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -1144,24 +1140,24 @@
         <v>650</v>
       </c>
       <c r="C25">
-        <v>1.1599999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="D25">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="E25">
-        <v>0.08</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="F25">
-        <v>-45</v>
+        <v>-157.5</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="0"/>
-        <v>0.68965517241379315</v>
+        <v>0.67105263157894735</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="1"/>
-        <v>6.8965517241379323E-2</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
@@ -1172,24 +1168,24 @@
         <v>700</v>
       </c>
       <c r="C26">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="D26">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="E26">
-        <v>9.5000000000000001E-2</v>
+        <v>0.112</v>
       </c>
       <c r="F26">
-        <v>45</v>
+        <v>-135</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="0"/>
-        <v>0.640625</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="1"/>
-        <v>7.421875E-2</v>
+        <v>6.9135802469135796E-2</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
@@ -1200,24 +1196,24 @@
         <v>750</v>
       </c>
       <c r="C27">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="D27">
-        <v>0.84</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E27">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F27">
-        <v>-60</v>
+        <v>-147</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>
-        <v>0.65625</v>
+        <v>0.67073170731707321</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="1"/>
-        <v>9.375E-2</v>
+        <v>7.926829268292683E-2</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
@@ -1228,24 +1224,24 @@
         <v>800</v>
       </c>
       <c r="C28">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="D28">
-        <v>0.9</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="E28">
-        <v>0.16</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="F28">
-        <v>-60</v>
+        <v>-157</v>
       </c>
       <c r="G28" s="3">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.65662650602409645</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="1"/>
-        <v>0.1142857142857143</v>
+        <v>8.6746987951807228E-2</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -1256,24 +1252,24 @@
         <v>850</v>
       </c>
       <c r="C29">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="D29">
-        <v>0.92</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="E29">
-        <v>0.192</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="F29">
-        <v>-60</v>
+        <v>-150</v>
       </c>
       <c r="G29" s="3">
         <f t="shared" si="0"/>
-        <v>0.63888888888888895</v>
+        <v>0.65662650602409645</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
@@ -1284,24 +1280,24 @@
         <v>900</v>
       </c>
       <c r="C30">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="D30">
-        <v>0.96</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="E30">
-        <v>0.216</v>
+        <v>0.188</v>
       </c>
       <c r="F30">
-        <v>-60</v>
+        <v>-135</v>
       </c>
       <c r="G30" s="3">
         <f t="shared" si="0"/>
-        <v>0.63157894736842102</v>
+        <v>0.64117647058823535</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" si="1"/>
-        <v>0.14210526315789473</v>
+        <v>0.11058823529411765</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -1312,24 +1308,24 @@
         <v>950</v>
       </c>
       <c r="C31">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="D31">
-        <v>1.04</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E31">
-        <v>0.25</v>
+        <v>0.216</v>
       </c>
       <c r="F31">
-        <v>54</v>
+        <v>-159</v>
       </c>
       <c r="G31" s="3">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.64367816091954033</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="1"/>
-        <v>0.15625</v>
+        <v>0.12413793103448276</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
@@ -1340,24 +1336,24 @@
         <v>1000</v>
       </c>
       <c r="C32">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="D32">
-        <v>1.08</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="E32">
-        <v>0.28799999999999998</v>
+        <v>0.248</v>
       </c>
       <c r="F32">
-        <v>-18</v>
+        <v>-151.19999999999999</v>
       </c>
       <c r="G32" s="3">
         <f t="shared" si="0"/>
-        <v>0.6428571428571429</v>
+        <v>0.64772727272727271</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" si="1"/>
-        <v>0.17142857142857143</v>
+        <v>0.1409090909090909</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
@@ -1368,24 +1364,24 @@
         <v>1500</v>
       </c>
       <c r="C33">
-        <v>0.92</v>
+        <v>1.38</v>
       </c>
       <c r="D33">
-        <v>1.04</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="E33">
-        <v>0.34</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="F33">
-        <v>90</v>
+        <v>-99.4</v>
       </c>
       <c r="G33" s="3">
         <f t="shared" si="0"/>
-        <v>1.1304347826086956</v>
+        <v>0.62028985507246381</v>
       </c>
       <c r="H33" s="3">
         <f t="shared" si="1"/>
-        <v>0.36956521739130438</v>
+        <v>0.4289855072463768</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
@@ -1396,24 +1392,24 @@
         <v>2000</v>
       </c>
       <c r="C34">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D34">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="E34">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E34">
-        <v>0.9</v>
-      </c>
       <c r="F34">
-        <v>72</v>
+        <v>-61.2</v>
       </c>
       <c r="G34" s="3">
         <f t="shared" si="0"/>
-        <v>0.46666666666666673</v>
+        <v>0.68</v>
       </c>
       <c r="H34" s="3">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.40000000000000008</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -1424,24 +1420,24 @@
         <v>2500</v>
       </c>
       <c r="C35">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="D35">
-        <v>0.26</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="F35">
-        <v>135</v>
+        <v>-58.5</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="0"/>
-        <v>0.29545454545454547</v>
+        <v>0.67272727272727273</v>
       </c>
       <c r="H35" s="3">
         <f t="shared" si="1"/>
-        <v>1.1363636363636365</v>
+        <v>0.40606060606060607</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
@@ -1452,24 +1448,24 @@
         <v>3000</v>
       </c>
       <c r="C36">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="D36">
-        <v>0.16400000000000001</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="E36">
-        <v>1.04</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="F36">
-        <v>103.6</v>
+        <v>-60</v>
       </c>
       <c r="G36" s="3">
         <f t="shared" si="0"/>
-        <v>0.21578947368421053</v>
+        <v>0.5636363636363636</v>
       </c>
       <c r="H36" s="3">
         <f t="shared" si="1"/>
-        <v>1.368421052631579</v>
+        <v>0.46666666666666662</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
@@ -1480,24 +1476,24 @@
         <v>3500</v>
       </c>
       <c r="C37">
-        <v>0.76</v>
+        <v>1.28</v>
       </c>
       <c r="D37">
-        <v>0.14000000000000001</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="E37">
-        <v>1.08</v>
+        <v>0.68</v>
       </c>
       <c r="F37">
-        <v>96.4</v>
+        <v>-57.8</v>
       </c>
       <c r="G37" s="3">
         <f t="shared" si="0"/>
-        <v>0.18421052631578949</v>
+        <v>0.41875000000000001</v>
       </c>
       <c r="H37" s="3">
         <f t="shared" si="1"/>
-        <v>1.4210526315789473</v>
+        <v>0.53125</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
@@ -1508,24 +1504,24 @@
         <v>4000</v>
       </c>
       <c r="C38">
-        <v>0.82</v>
+        <v>1.22</v>
       </c>
       <c r="D38">
-        <v>0.13200000000000001</v>
+        <v>0.376</v>
       </c>
       <c r="E38">
-        <v>1.08</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="F38">
-        <v>108</v>
+        <v>-50.4</v>
       </c>
       <c r="G38" s="3">
         <f t="shared" si="0"/>
-        <v>0.16097560975609757</v>
+        <v>0.30819672131147541</v>
       </c>
       <c r="H38" s="3">
         <f t="shared" si="1"/>
-        <v>1.3170731707317074</v>
+        <v>0.57049180327868854</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
@@ -1536,24 +1532,24 @@
         <v>4500</v>
       </c>
       <c r="C39">
-        <v>0.88</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D39">
-        <v>0.13200000000000001</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="E39">
-        <v>1.2</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="F39">
-        <v>122</v>
+        <v>-40.9</v>
       </c>
       <c r="G39" s="3">
         <f t="shared" si="0"/>
-        <v>0.15</v>
+        <v>0.22068965517241382</v>
       </c>
       <c r="H39" s="3">
         <f t="shared" si="1"/>
-        <v>1.3636363636363635</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
@@ -1564,24 +1560,24 @@
         <v>5000</v>
       </c>
       <c r="C40">
-        <v>0.98</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D40">
-        <v>0.128</v>
+        <v>0.184</v>
       </c>
       <c r="E40">
-        <v>1.24</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="F40">
-        <v>99</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="G40" s="3">
         <f t="shared" si="0"/>
-        <v>0.1306122448979592</v>
+        <v>0.16727272727272727</v>
       </c>
       <c r="H40" s="3">
         <f t="shared" si="1"/>
-        <v>1.2653061224489797</v>
+        <v>0.62545454545454537</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
@@ -1592,24 +1588,24 @@
         <v>5500</v>
       </c>
       <c r="C41">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="D41">
-        <v>0.12</v>
+        <v>0.128</v>
       </c>
       <c r="E41">
-        <v>1.28</v>
+        <v>0.68</v>
       </c>
       <c r="F41">
-        <v>110</v>
+        <v>-40.799999999999997</v>
       </c>
       <c r="G41" s="3">
         <f t="shared" si="0"/>
-        <v>0.11320754716981131</v>
+        <v>0.12307692307692307</v>
       </c>
       <c r="H41" s="3">
         <f t="shared" si="1"/>
-        <v>1.2075471698113207</v>
+        <v>0.65384615384615385</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
@@ -1620,24 +1616,24 @@
         <v>6000</v>
       </c>
       <c r="C42">
-        <v>1.1200000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="D42">
-        <v>0.12</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="E42">
-        <v>1.32</v>
+        <v>0.68</v>
       </c>
       <c r="F42">
-        <v>116.5</v>
+        <v>-38</v>
       </c>
       <c r="G42" s="3">
         <f t="shared" si="0"/>
-        <v>0.10714285714285712</v>
+        <v>9.7959183673469397E-2</v>
       </c>
       <c r="H42" s="3">
         <f t="shared" si="1"/>
-        <v>1.1785714285714286</v>
+        <v>0.69387755102040827</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
@@ -1648,24 +1644,24 @@
         <v>6500</v>
       </c>
       <c r="C43">
-        <v>1.18</v>
+        <v>0.98</v>
       </c>
       <c r="D43">
-        <v>0.16</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="E43">
-        <v>1.32</v>
+        <v>0.68</v>
       </c>
       <c r="F43">
-        <v>108</v>
+        <v>-36.4</v>
       </c>
       <c r="G43" s="3">
         <f t="shared" si="0"/>
-        <v>0.13559322033898305</v>
+        <v>7.7551020408163265E-2</v>
       </c>
       <c r="H43" s="3">
         <f t="shared" si="1"/>
-        <v>1.1186440677966103</v>
+        <v>0.69387755102040827</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
@@ -1676,24 +1672,24 @@
         <v>7000</v>
       </c>
       <c r="C44">
-        <v>1.28</v>
+        <v>0.98</v>
       </c>
       <c r="D44">
-        <v>0.104</v>
+        <v>0.06</v>
       </c>
       <c r="E44">
-        <v>1.48</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="F44">
-        <v>108</v>
+        <v>-34.1</v>
       </c>
       <c r="G44" s="3">
         <f t="shared" si="0"/>
-        <v>8.1249999999999989E-2</v>
+        <v>6.1224489795918366E-2</v>
       </c>
       <c r="H44" s="3">
         <f t="shared" si="1"/>
-        <v>1.15625</v>
+        <v>0.70204081632653059</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
@@ -1704,24 +1700,24 @@
         <v>7500</v>
       </c>
       <c r="C45">
-        <v>1.32</v>
+        <v>0.98</v>
       </c>
       <c r="D45">
-        <v>0.1</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="E45">
-        <v>1.48</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="F45">
-        <v>115.7</v>
+        <v>-32.5</v>
       </c>
       <c r="G45" s="3">
         <f t="shared" si="0"/>
-        <v>7.575757575757576E-2</v>
+        <v>5.3061224489795916E-2</v>
       </c>
       <c r="H45" s="3">
         <f t="shared" si="1"/>
-        <v>1.1212121212121211</v>
+        <v>0.70204081632653059</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
@@ -1732,24 +1728,24 @@
         <v>8000</v>
       </c>
       <c r="C46">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="D46">
-        <v>9.1999999999999998E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="E46">
-        <v>1.52</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="F46">
-        <v>125</v>
+        <v>-33.299999999999997</v>
       </c>
       <c r="G46" s="3">
         <f t="shared" si="0"/>
-        <v>6.5714285714285711E-2</v>
+        <v>0.05</v>
       </c>
       <c r="H46" s="3">
         <f t="shared" si="1"/>
-        <v>1.0857142857142859</v>
+        <v>0.72499999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
@@ -1760,24 +1756,24 @@
         <v>8500</v>
       </c>
       <c r="C47">
-        <v>1.46</v>
+        <v>0.94</v>
       </c>
       <c r="D47">
-        <v>8.7999999999999995E-2</v>
+        <v>0.04</v>
       </c>
       <c r="E47">
-        <v>1.56</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="F47">
-        <v>105</v>
+        <v>-26.1</v>
       </c>
       <c r="G47" s="3">
         <f t="shared" si="0"/>
-        <v>6.0273972602739721E-2</v>
+        <v>4.2553191489361708E-2</v>
       </c>
       <c r="H47" s="3">
         <f t="shared" si="1"/>
-        <v>1.0684931506849316</v>
+        <v>0.74042553191489358</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
@@ -1788,24 +1784,24 @@
         <v>9000</v>
       </c>
       <c r="C48">
-        <v>1.48</v>
+        <v>0.94</v>
       </c>
       <c r="D48">
-        <v>8.4000000000000005E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="E48">
-        <v>1.64</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="F48">
-        <v>147</v>
+        <v>-21.1</v>
       </c>
       <c r="G48" s="3">
         <f t="shared" si="0"/>
-        <v>5.675675675675676E-2</v>
+        <v>3.4042553191489362E-2</v>
       </c>
       <c r="H48" s="3">
         <f t="shared" si="1"/>
-        <v>1.1081081081081081</v>
+        <v>0.74893617021276593</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
@@ -1816,24 +1812,24 @@
         <v>9500</v>
       </c>
       <c r="C49">
-        <v>1.56</v>
+        <v>0.96</v>
       </c>
       <c r="D49">
-        <v>7.5999999999999998E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="E49">
-        <v>1.72</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="F49">
-        <v>162</v>
+        <v>-25.3</v>
       </c>
       <c r="G49" s="3">
         <f t="shared" si="0"/>
-        <v>4.8717948717948718E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H49" s="3">
         <f t="shared" si="1"/>
-        <v>1.1025641025641024</v>
+        <v>0.7416666666666667</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
@@ -1844,24 +1840,24 @@
         <v>10000</v>
       </c>
       <c r="C50">
-        <v>1.6</v>
+        <v>0.98</v>
       </c>
       <c r="D50">
-        <v>7.5999999999999998E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E50">
-        <v>1.72</v>
+        <v>0.72</v>
       </c>
       <c r="F50">
-        <v>90</v>
+        <v>-19.399999999999999</v>
       </c>
       <c r="G50" s="3">
         <f t="shared" si="0"/>
-        <v>4.7499999999999994E-2</v>
+        <v>2.0408163265306124E-2</v>
       </c>
       <c r="H50" s="3">
         <f t="shared" si="1"/>
-        <v>1.075</v>
+        <v>0.73469387755102045</v>
       </c>
     </row>
   </sheetData>
